--- a/reporte_analizado.xlsx
+++ b/reporte_analizado.xlsx
@@ -156,12 +156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Resumen'!$A$2:$A$1</f>
+              <f>'Resumen'!$A$2</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Resumen'!$B$2:$B$1</f>
+              <f>'Resumen'!$B$2</f>
             </numRef>
           </val>
         </ser>
@@ -182,6 +182,211 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -497,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,8 +752,329 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-11-22 14:59:23</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2025-11-22 14:59:28</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 14:59:28
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-11-22 14:59:29</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2025-11-22 14:59:31</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 14:59:31
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:32:36</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:32:39</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 15:32:39
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:32:42</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:32:43</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 15:32:43
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:32:49</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:32:53</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 15:32:53
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:32:59</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:33:02</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 15:33:02
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:33:34</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:33:34</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 15:33:34
+Usuario: admin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:33:36</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:33:36</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 15:33:36
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -558,7 +1084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,6 +1097,16 @@
         <is>
           <t>Incidentes</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/reporte_analizado.xlsx
+++ b/reporte_analizado.xlsx
@@ -373,6 +373,406 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3810000" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -702,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1071,6 +1471,646 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:49:48</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:49:52</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>13</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 15:49:52
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:49:54</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:49:59</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>17</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 15:49:59
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:49:57</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2025-11-22 15:49:57</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 15:49:57
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-11-22 16:13:02</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2025-11-22 16:13:07</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 16:13:07
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-11-22 16:13:04</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2025-11-22 16:13:05</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 16:13:05
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:15:27</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:15:28</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 17:15:28
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>17</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:15:29</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:15:31</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 17:15:31
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:22:56</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:22:57</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 17:22:57
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:47:12</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:47:14</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 17:47:14
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>21</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:47:15</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:47:18</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 17:47:18
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>22</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:47:18</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:47:22</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>9</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 17:47:22
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>23</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:47:21</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:47:25</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 17:47:25
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>24</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:47:24</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2025-11-22 17:47:28</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 17:47:28
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>25</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-11-22 18:34:58</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2025-11-22 18:35:03</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 18:35:03
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>26</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-11-22 18:35:01</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2025-11-22 18:35:02</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 18:35:02
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>27</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-11-22 18:35:04</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2025-11-22 18:35:06</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 18:35:06
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1106,7 +2146,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/reporte_analizado.xlsx
+++ b/reporte_analizado.xlsx
@@ -182,611 +182,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId23"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3810000" cy="2143125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId24"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1102,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2112,9 +1507,648 @@
       </c>
       <c r="I25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>28</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-11-22 19:37:40</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2025-11-22 19:37:43</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 19:37:43
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>30</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-11-22 19:37:48</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2025-11-22 19:37:53</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>10</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 19:37:53
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>31</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-11-22 19:37:53</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2025-11-22 19:37:56</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 19:37:56
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>32</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-11-22 19:37:55</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2025-11-22 19:37:58</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 19:37:58
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>34</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-11-22 19:47:08</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2025-11-22 19:47:11</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>9</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 19:47:11
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>36</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-11-22 20:39:06</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2025-11-22 20:39:10</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 20:39:10
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>38</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-11-22 20:41:11</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2025-11-22 20:41:13</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>7</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 20:41:13
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>39</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-11-22 20:41:16</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2025-11-22 20:41:16</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 20:41:16
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>40</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-11-22 20:41:17</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2025-11-22 20:41:20</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>11</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 20:41:20
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>41</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-11-22 20:56:35</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2025-11-22 20:56:35</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 20:56:35
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>42</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025-11-22 20:56:36</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2025-11-22 20:56:38</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>7</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 20:56:38
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>43</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-11-22 21:04:59</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2025-11-22 21:05:00</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 21:05:00
+Usuario: admin</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>44</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-11-22 21:11:34</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2025-11-22 21:11:37</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>8</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 21:11:37
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>46</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Falta Chaleco</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025-11-22 21:46:50</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2025-11-22 21:46:51</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Falta Chaleco — Camera_1 2025-11-22 21:46:51
+Usuario: admin</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>48</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-11-22 21:47:03</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2025-11-22 21:47:03</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 21:47:03
+Usuario: admin</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>49</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Falta Casco</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025-11-22 21:47:04</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2025-11-22 21:47:06</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>9</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Falta Casco — Camera_1 2025-11-22 21:47:06
+Usuario: unknown</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2146,7 +2180,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
